--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,490 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>57s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>If you knew [過去形/事実]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>...if you knew how much I love...</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>（もし）〜だと知っていたら</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1:04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[主語] thought that would [動詞]</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>He thought that would cheer me up.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[主語]はそれが[動詞]すると思った</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1:04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cheer [人] up</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>...cheer me up.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[人]を元気づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1:08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>What goes on in [人]'s head?</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Just what goes on in his head?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[人]の頭の中はどうなってるの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1:12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ask [人] for [モノ/事]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>...asking me for your phone number...</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[人]に[モノ/事]を求める</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>have the guts to [動詞]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>He didn't have the guts to ask...</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[動詞]する度胸がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1:24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Who's up for [名詞/動名詞]?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yo, who's up for some bad singing?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[名詞/動名詞]したい人？</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>What a steal!</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Half off, two hours. What a steal.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>激安だ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1:35</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>I think I'm gonna pass.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ah, I think I'm gonna pass.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>（今回は）やめておくよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1:56</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[人/モノ] sounded so [形容詞]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oh, he sounded so depressed.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[人/モノ]がとても[形容詞]に聞こえた</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1:59</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Then again...</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Then again, that's kind of his thing.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>そうは言っても</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1:59</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>That's kind of [人]'s thing.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>...that's kind of his thing.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>それは[人]のいつものやつだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2:07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[主語] has to be [名詞/形容詞]</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>He has to be.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[主語]は絶対に[名詞/形容詞]だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2:12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pick up [モノ/事]</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Does your nerd alert pick up anything?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[モノ/事]を感知する</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2:18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>I don't even know if [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>I don't even know if Miyamura has...</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[主語が〜する]かどうかすら分からない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2:20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>gotta [動詞]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gotta run.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[動詞]しなきゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2:24</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>It feels like [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>It feels like she hurries home every day.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[主語が〜している]気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2:28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[名詞] or something</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Must be a boyfriend or something.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[名詞]か何か</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2:31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>way [形容詞]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Well, she's way popular.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>めちゃくちゃ[形容詞]だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2:54</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Got it.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Got it.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>了解</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2:55</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>I'll handle [モノ/事]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>I'll handle dinner.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[モノ/事]は私が処理するよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2:57</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[モノ/事] sucks.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Overtime sucks, I know.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[モノ/事]は最悪だ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>That's all for [today / now]</t>
+          <t>That's all for [名詞]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[ today / now ] はこれで終わり / 以上だ</t>
+          <t>[名詞]はこれで以上だ</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[モノ/事] will eat up my time</t>
+          <t>[主語] will eat up [モノ/事]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[モノ/事]が時間を食いつぶす・費やす</t>
+          <t>[主語]が[モノ/事]を食いつぶす</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most of my [名詞]</t>
+          <t>most of [名詞]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[名詞]の大半 / ほとんど</t>
+          <t>[名詞]の大半</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[人]に[動詞]するよう促す / 勧める</t>
+          <t>[人]に[動詞]するよう勧める</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>while you still can</t>
+          <t>while [主語+動詞]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>（あなたが）できるうちに / できる間は</t>
+          <t>[主語]が[動詞]できるうちに</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>喜んで[動詞]しますよ / （もし〜なら）〜したいところです</t>
+          <t>喜んで[動詞]する</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why would you [動詞]?</t>
+          <t>Why would [主語] [動詞]?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>なんで（あなたが）[動詞]なんてするの？ / なぜ〜するわけ？</t>
+          <t>なんで[主語]が[動詞]なんてするの？</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>（[人]に）ついて行く / 同行する</t>
+          <t>（[人]に）ついて行く</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[形容詞]な態度をとるな / 〜にするな</t>
+          <t>[形容詞]な態度をとるな</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[モノ/事]が関わっている / 絡んでいる</t>
+          <t>[モノ/事]が関わっているとき</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大人の監視 / 監督が必要だ</t>
+          <t>大人の監視が必要だ</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>（それは）理にかなっている / 納得だ / 確かにそうだね</t>
+          <t>それは理にかなっている</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[行動/発言] is baffling</t>
+          <t>[主語] is baffling</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[行動/発言]が理解不能だ / 呆れ果てる</t>
+          <t>[主語]が理解不能だ</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>お墨付きの[名詞] / 誰もが認める[名詞]</t>
+          <t>誰もが認める[名詞]</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>馬鹿なこと / くだらないこと</t>
+          <t>くだらないこと</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>元気を出して / うつむかないで</t>
+          <t>元気を出して</t>
         </is>
       </c>
     </row>

--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>while [主語+動詞]</t>
+          <t>while [主語] still can</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[主語]が[動詞]できるうちに</t>
+          <t>[主語]ができるうちに</t>
         </is>
       </c>
     </row>
@@ -1299,6 +1299,490 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>[モノ/事]は最悪だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3:03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>should probably get going</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>I should probably get going.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>そろそろ行かなくちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3:07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>have been [動詞ing]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>We've been waiting for you.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ずっと[動詞]し続けている</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3:07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wait for [人/モノ]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>We've been waiting for you.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[人/モノ]を待つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3:16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>hit up [場所/人]</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Let's hit up that store...</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[場所/人]に行く・連絡する</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3:16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>while [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>...while we're here.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[主語]が[動詞]している間に</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3:19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Why not?</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Why not?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>いいじゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>on [人]'s day off</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>...working on her day off.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[人]の休日に</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5:03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>too [形容詞] for [人]'s own good</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>...she's too nice for her own good.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[形容詞]すぎて本人のためにならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5:07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>I wish [主語] would [動詞]</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>I wish she'd learn how to...</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[主語]が[動詞]してくれたらいいのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5:07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>say [言葉] to [人]</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>...how to say no to people.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[人]に[言葉]を言う</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5:18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[モノ/事] happen to [人]</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>...what happened to your little nose?</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[人]に[モノ/事]が起こる</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>5:21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fall down</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>I fell down.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>転ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5:29</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>have / get [モノ/事] taken care of</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>...since you've got it taken care of.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[モノ/事]を片付けてもらう</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>5:34</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>cause [人] trouble</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hope he didn't cause you too much trouble.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[人]に迷惑をかける</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5:45</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>be in a hurry</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>...if you're not in any sort of hurry...</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>急いでいる</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5:45</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>any sort of [名詞]</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>...if you're not in any sort of hurry...</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>何らかの[名詞]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5:48</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>more than [形容詞]</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>...you're more than welcome to stay...</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>十分に[形容詞]だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>5:48</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>for a while</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>...to stay for a while.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>しばらくの間</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>5:52</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[人]'s way of [動名詞ing]</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>This will be my way of saying thanks.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[人]なりの[動詞]する方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>5:56</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>[主語] spook [人]</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>...because this dog spooked him.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[主語]が[人]を驚かせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5:59</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>I appreciate [人] [動名詞ing]</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>I appreciate you helping him out.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[人]が[動詞]してくれて感謝する</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5:59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>help [人] out</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>...helping him out.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[人]を助ける</t>
         </is>
       </c>
     </row>

--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1786,6 +1786,358 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6:01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>appreciate [人] for [名詞/動名詞]</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>...I appreciate you for treating me.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[人]の[名詞/動名詞]に感謝する</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6:03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Why do you [動詞] if [主語+動詞]?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Why do you drink coffee if it tastes so gross?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[主語が〜]なら、なぜ[動詞]するの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6:06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ask myself the same thing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>I ask myself the same thing.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>自分でもそう思ってる</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>6:09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>introduce [自分]</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>He introduced himself...</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>自己紹介する</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6:09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>[言葉/行動] and everything</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>He introduced himself and everything.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[言葉/行動]やら何やらすべて</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6:12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>That's nice of [人] to [動詞]</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>That's nice of you to say.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[人]が[動詞]してくれて優しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6:12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>a real handful</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>He's a real handful...</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>本当に手に負えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6:17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>[主語] is what's really [形容詞]</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>...housework is what's really impressive.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[主語]こそが本当に[形容詞]なことだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6:21</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Never would have guessed.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Never would have guessed, Hori.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>全く予想もつかなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>6:28</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>How'd you know that?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>...how'd you know that?</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>なんでそれ知ってるの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>6:32</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>the same [名詞] as [人/モノ]</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>...the same school as me?</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[人/モノ]と同じ[名詞]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6:36</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Are you being [形容詞] right now?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Are you being serious right now?</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>今[形容詞]な態度をとってるの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6:48</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>That can't be [人/モノ].</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>That can't be the same person.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>それが[人/モノ]なはずがない</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6:50</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>[主語] doesn't make sense anymore</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>...the world doesn't make sense anymore.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[主語]がもう意味をなさない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6:52</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>one of the [最上級] [複数名詞]</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>...one of the weirdest faces...</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>最も[形容詞]な[名詞]の一つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6:52</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>in the history of [名詞]</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>...in the history of weird faces.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[名詞]の歴史の中で</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pick up [モノ/事]</t>
+          <t>pick up [信号/気配]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[モノ/事]を感知する</t>
+          <t>[信号/気配]を感知する</t>
         </is>
       </c>
     </row>
@@ -2135,6 +2135,710 @@
       <c r="D78" t="inlineStr">
         <is>
           <t>[名詞]の歴史の中で</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7:07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Got a sec?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Miyamura, got a sec?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ちょっと時間ある？</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7:11</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>come over to [場所]</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>...come over to your house again?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[場所]へ遊びに来る</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7:17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>save [人] from [モノ/事]</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>...saved him from the dog...</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[人]を[モノ/事]から救う</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7:22</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>pick up [モノ]</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>I'll pick up a picture book...</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[モノ]を買ってくる</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7:24</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>[主語] will be enough</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>...showing up will be enough...</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[主語]で十分だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7:28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>What a relief!</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>What a relief.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ホッとした</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7:28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>break [人]'s heart</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>...break Sota's heart.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[人]をひどく傷つける</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7:37</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>the fact that [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>By the fact that you sought me out...</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[主語が〜する]という事実</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7:37</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>seek [人] out</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>...you sought me out...</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[人]を探し出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7:39</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>after [過去の事/日] and all</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>...after yesterday and all.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[過去の事/日]もあった後で</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7:41</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>for sure</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>...I thought for sure you'd avoid me.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>間違いなく</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7:44</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>that way</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>...react that way?</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>そんな風に</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7:51</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>It freaks [人] out to [動詞]</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>It freaked me out to see...</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[動詞]して[人]はびっくりする</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7:51</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>a different side of [人]</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>...a different side of you...</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[人]の意外な一面</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7:54</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>out of [場所]</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>...out of school, too.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[場所]の外で</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7:56</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>a silly reason</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>...a pretty silly reason...</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>くだらない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7:56</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>straight up [動詞]</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>...to straight up avoid you.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>あからさまに[動詞]する</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8:02</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>be not used to [動名詞/名詞]</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>I'm just not used to hearing...</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[動名詞/名詞]に慣れていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>8:12</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What's with [モノ/事]?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>What's with the look?</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[モノ/事]は一体どうしたの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>8:14</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>notice how [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>I just noticed how nice your smile is.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[主語が〜であるか]に気づく</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>8:16</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>wear [髪] up</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>You should wear your hair up...</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[髪]をアップにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>8:16</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>more often</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>...more often.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>もっと頻繁に</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>8:16</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>lose [モノ]</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Maybe lose the glasses, too.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[モノ]を外す</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>8:19</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Don't you think?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Don't you think?</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>そう思わない？</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>8:24</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>quite a few</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>You do have quite a few.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>かなりの数</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>8:24</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>What's the grand total?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>So what's the grand total?</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>合計でいくつ（いくら）？</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>8:27</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>up to [数値]</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>It's up to nine.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>最大で[数値]まで</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>8:27</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>along with [モノ/人]</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>...along with the one on my lip.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[モノ/人]と一緒に</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>8:33</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>agree with [人]</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>My mom would agree with you.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[人]に同意する</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>8:40</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>be into [モノ/事]</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>...I'm not into that moe nonsense.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[モノ/事]にハマっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>8:51</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>like you wouldn't believe</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>...hurt like you wouldn't believe.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>信じられないほど（〜だ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>8:54</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>back in [過去の時期]</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>...back in middle school.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[過去の時期]の頃に</t>
         </is>
       </c>
     </row>

--- a/data/horimiya.xlsx
+++ b/data/horimiya.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2842,6 +2842,270 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9:04</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>a straight-A [名詞]</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>...You're like a straight-A queen.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>成績がオールAの[名詞]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>9:09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>What's incredible is [主語+動詞]</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>What's incredible is how a quiet guy...</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>驚きなのは[主語が〜する]ことだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9:12</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Is that the rule?</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Is that the rule?</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>それがルールなの？</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9:17</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>[人]'s initial impression of [人/モノ]</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>my initial impression of him</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[人]が[人/モノ]に抱いた第一印象</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9:18</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>couldn't have been further from [名詞/実態]</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>...couldn't have been further from the person...</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[名詞/実態]とは全く違っていた</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9:24</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>[モノ] is on sale</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Eggs are on sale tomorrow...</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[モノ]がセール中だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9:39</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>[事/モノ] lasts till [時間]</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>...only lasts till 4:00 p.m.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[事/モノ]が[時間]まで続く</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9:42</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>I've got this.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>I mean, I've got this.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>私に任せて</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9:43</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>stand in [人]'s way</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Nothing's gonna stand in my way...</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>[人]の行く手を阻む</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9:47</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>What are the odds?</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>But what are the odds?</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>まさかそんなことがあるなんて</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9:51</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>report to [場所]</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>All committee members please report to...</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[場所]に集合する</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>9:54</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>be called in for [名詞]</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>You're being called for an emergency meeting.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[名詞]のために呼び出される</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
